--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -21825,7 +21825,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -22901,7 +22901,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -24515,7 +24515,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -26129,7 +26129,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -26667,7 +26667,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -27598,7 +27598,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -29212,7 +29212,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -29750,7 +29750,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -31902,7 +31902,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -32440,7 +32440,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN178" t="b">

--- a/diseases/d168/2000-2004.xlsx
+++ b/diseases/d168/2000-2004.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25581,7 +25581,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26119,7 +26119,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30278,7 +30278,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -32430,7 +32430,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -32968,7 +32968,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
